--- a/outputs/first100/asr_report.xlsx
+++ b/outputs/first100/asr_report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="27">
   <si>
     <t>model</t>
   </si>
@@ -36,6 +36,9 @@
     <t>qwen_audio</t>
   </si>
   <si>
+    <t>podlodka</t>
+  </si>
+  <si>
     <t>gemma</t>
   </si>
   <si>
@@ -43,9 +46,6 @@
   </si>
   <si>
     <t>gigaam</t>
-  </si>
-  <si>
-    <t>podlodka</t>
   </si>
   <si>
     <t>golos_farfield</t>
@@ -220,22 +220,25 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>models_summary!$A$2:$A$6</c:f>
+              <c:f>models_summary!$A$2:$A$7</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>gigaam</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>podlodka</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>whisper</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>t_one</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>qwen_audio</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>gemma</c:v>
                 </c:pt>
               </c:strCache>
@@ -243,23 +246,26 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>models_summary!$C$2:$C$6</c:f>
+              <c:f>models_summary!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0.07733205723174937</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.09009244719999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.0963357483870714</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>0.1017868391065072</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>0.6269819889146704</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>0.8107173190318028</c:v>
                 </c:pt>
               </c:numCache>
@@ -648,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -670,7 +676,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0.0758793003469506</v>
@@ -684,7 +690,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>0.4228087050189174</v>
@@ -698,7 +704,7 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.2323769898604649</v>
+        <v>0.09009244719999999</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -706,57 +712,57 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>0.1354387257394058</v>
+        <v>0.2323769898604649</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0.2086631101782617</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
+        <v>0.1354387257394058</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7">
-        <v>1.38731142594779</v>
+        <v>0.2086631101782617</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8">
-        <v>0.06935698981153519</v>
+        <v>1.38731142594779</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9">
-        <v>1.207452592301077</v>
+        <v>0.06935698981153519</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -767,54 +773,54 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.1315419709359103</v>
+        <v>1.207452592301077</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>0.1027865118494669</v>
-      </c>
-      <c r="D11" t="s">
-        <v>19</v>
+        <v>0.1315419709359103</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12">
-        <v>0.6451614902183401</v>
+        <v>0.1027865118494669</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13">
-        <v>0.0569488535940136</v>
+        <v>0.6451614902183401</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14">
-        <v>0.7193696830116254</v>
+        <v>0.0569488535940136</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -825,54 +831,54 @@
         <v>11</v>
       </c>
       <c r="C15">
-        <v>0.0481800055224305</v>
+        <v>0.7193696830116254</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16">
-        <v>0.1623050360302916</v>
-      </c>
-      <c r="D16" t="s">
-        <v>19</v>
+        <v>0.0481800055224305</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
         <v>12</v>
       </c>
       <c r="C17">
-        <v>0.8665847061955988</v>
+        <v>0.1623050360302916</v>
+      </c>
+      <c r="D17" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
       </c>
       <c r="C18">
-        <v>0.1012309764608291</v>
+        <v>0.8665847061955988</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19">
-        <v>0.8818744382153239</v>
+        <v>0.1012309764608291</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -883,54 +889,54 @@
         <v>12</v>
       </c>
       <c r="C20">
-        <v>0.1239483357364959</v>
+        <v>0.8818744382153239</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>0.0431007612221763</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
+        <v>0.1239483357364959</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
       <c r="C22">
-        <v>0.3144735513157043</v>
+        <v>0.0431007612221763</v>
+      </c>
+      <c r="D22" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23">
-        <v>0.0856398284648606</v>
+        <v>0.3144735513157043</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24">
-        <v>0.108476024166053</v>
+        <v>0.0856398284648606</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -941,54 +947,54 @@
         <v>13</v>
       </c>
       <c r="C25">
-        <v>0.1169500122170223</v>
+        <v>0.108476024166053</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26">
-        <v>0.1321356768181972</v>
-      </c>
-      <c r="D26" t="s">
-        <v>19</v>
+        <v>0.1169500122170223</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
       <c r="C27">
-        <v>0.6201261735947166</v>
+        <v>0.1321356768181972</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
       <c r="C28">
-        <v>0.181590372425242</v>
+        <v>0.6201261735947166</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29">
-        <v>1.714538576347668</v>
+        <v>0.181590372425242</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -999,54 +1005,54 @@
         <v>14</v>
       </c>
       <c r="C30">
-        <v>0.1571001698350601</v>
+        <v>1.714538576347668</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>0.1206278569914933</v>
-      </c>
-      <c r="D31" t="s">
-        <v>19</v>
+        <v>0.1571001698350601</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.398678369890491</v>
+        <v>0.1206278569914933</v>
+      </c>
+      <c r="D32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
       <c r="C33">
-        <v>0.0773561455379637</v>
+        <v>0.398678369890491</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34">
-        <v>1.351668589547377</v>
+        <v>0.0773561455379637</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1057,54 +1063,54 @@
         <v>15</v>
       </c>
       <c r="C35">
-        <v>0.08837812019630201</v>
+        <v>1.351668589547377</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C36">
-        <v>0.0198138510140105</v>
-      </c>
-      <c r="D36" t="s">
-        <v>19</v>
+        <v>0.08837812019630201</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37">
-        <v>0.3679134828865326</v>
+        <v>0.0198138510140105</v>
+      </c>
+      <c r="D37" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38">
-        <v>0.0542524141238774</v>
+        <v>0.3679134828865326</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39">
-        <v>0.3746726475183648</v>
+        <v>0.0542524141238774</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1115,54 +1121,54 @@
         <v>16</v>
       </c>
       <c r="C40">
-        <v>0.0844663616061808</v>
+        <v>0.3746726475183648</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41">
-        <v>0.07189667795728399</v>
-      </c>
-      <c r="D41" t="s">
-        <v>19</v>
+        <v>0.0844663616061808</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
       </c>
       <c r="C42">
-        <v>0.6796962577265608</v>
+        <v>0.07189667795728399</v>
+      </c>
+      <c r="D42" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
       </c>
       <c r="C43">
-        <v>0.0539121372454705</v>
+        <v>0.6796962577265608</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
       </c>
       <c r="C44">
-        <v>1.204716075170621</v>
+        <v>0.0539121372454705</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1173,54 +1179,54 @@
         <v>17</v>
       </c>
       <c r="C45">
-        <v>0.091511070298949</v>
+        <v>1.204716075170621</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46">
-        <v>0.0261487014625819</v>
-      </c>
-      <c r="D46" t="s">
-        <v>19</v>
+        <v>0.091511070298949</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B47" t="s">
         <v>18</v>
       </c>
       <c r="C47">
-        <v>0.5670657263520529</v>
+        <v>0.0261487014625819</v>
+      </c>
+      <c r="D47" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
         <v>18</v>
       </c>
       <c r="C48">
-        <v>0.0157007974219522</v>
+        <v>0.5670657263520529</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
       </c>
       <c r="C49">
-        <v>0.3120275741794529</v>
+        <v>0.0157007974219522</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1231,6 +1237,17 @@
         <v>18</v>
       </c>
       <c r="C50">
+        <v>0.3120275741794529</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51">
         <v>0.0403536189773151</v>
       </c>
     </row>
@@ -1241,10 +1258,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1255,33 +1272,36 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>1.351668589547377</v>
@@ -1289,34 +1309,34 @@
       <c r="C2">
         <v>0.108476024166053</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>1.207452592301077</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.2323769898604649</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1.714538576347668</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.3120275741794529</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.7193696830116254</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.8818744382153239</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>1.204716075170621</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.3746726475183648</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0.0773561455379637</v>
@@ -1324,140 +1344,148 @@
       <c r="C3">
         <v>0.0856398284648606</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.06935698981153519</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.181590372425242</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.0157007974219522</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.0569488535940136</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.1012309764608291</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.0539121372454705</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.0542524141238774</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>0.09009244719999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>0.398678369890491</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>0.3144735513157043</v>
       </c>
-      <c r="D4">
+      <c r="E5">
         <v>1.38731142594779</v>
       </c>
-      <c r="E4">
+      <c r="F5">
         <v>0.4228087050189174</v>
       </c>
-      <c r="F4">
+      <c r="G5">
         <v>0.6201261735947166</v>
       </c>
-      <c r="G4">
+      <c r="H5">
         <v>0.5670657263520529</v>
       </c>
-      <c r="H4">
+      <c r="I5">
         <v>0.6451614902183401</v>
       </c>
-      <c r="I4">
+      <c r="J5">
         <v>0.8665847061955988</v>
       </c>
-      <c r="J4">
+      <c r="K5">
         <v>0.6796962577265608</v>
       </c>
-      <c r="K4">
+      <c r="L5">
         <v>0.3679134828865326</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>0.08837812019630201</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>0.1169500122170223</v>
       </c>
-      <c r="D5">
+      <c r="E6">
         <v>0.1315419709359103</v>
       </c>
-      <c r="E5">
+      <c r="F6">
         <v>0.1354387257394058</v>
       </c>
-      <c r="F5">
+      <c r="G6">
         <v>0.1571001698350601</v>
       </c>
-      <c r="G5">
+      <c r="H6">
         <v>0.0403536189773151</v>
       </c>
-      <c r="H5">
+      <c r="I6">
         <v>0.0481800055224305</v>
       </c>
-      <c r="I5">
+      <c r="J6">
         <v>0.1239483357364959</v>
       </c>
-      <c r="J5">
+      <c r="K6">
         <v>0.091511070298949</v>
       </c>
-      <c r="K5">
+      <c r="L6">
         <v>0.0844663616061808</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>0.1206278569914933</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>0.0431007612221763</v>
       </c>
-      <c r="D6">
+      <c r="E7">
         <v>0.2086631101782617</v>
       </c>
-      <c r="E6">
+      <c r="F7">
         <v>0.0758793003469506</v>
       </c>
-      <c r="F6">
+      <c r="G7">
         <v>0.1321356768181972</v>
       </c>
-      <c r="G6">
+      <c r="H7">
         <v>0.0261487014625819</v>
       </c>
-      <c r="H6">
+      <c r="I7">
         <v>0.1027865118494669</v>
       </c>
-      <c r="I6">
+      <c r="J7">
         <v>0.1623050360302916</v>
       </c>
-      <c r="J6">
+      <c r="K7">
         <v>0.07189667795728399</v>
       </c>
-      <c r="K6">
+      <c r="L7">
         <v>0.0198138510140105</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B6">
+  <conditionalFormatting sqref="B2:B7">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(B2:B6),B2:B6,0)+1&amp;"C2",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C2",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(B2:B7),B2:B7,0)+1&amp;"C2",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C2",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:K6">
+  <conditionalFormatting sqref="B2:L7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1469,49 +1497,54 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C7">
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(C2:C6),C2:C6,0)+1&amp;"C3",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C3",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(C2:C7),C2:C7,0)+1&amp;"C3",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C3",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="D2:D7">
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(D2:D6),D2:D6,0)+1&amp;"C4",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C4",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(D2:D7),D2:D7,0)+1&amp;"C4",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C4",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E6">
+  <conditionalFormatting sqref="E2:E7">
     <cfRule type="expression" dxfId="0" priority="5">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(E2:E6),E2:E6,0)+1&amp;"C5",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C5",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(E2:E7),E2:E7,0)+1&amp;"C5",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C5",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
+  <conditionalFormatting sqref="F2:F7">
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(F2:F6),F2:F6,0)+1&amp;"C6",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C6",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(F2:F7),F2:F7,0)+1&amp;"C6",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C6",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="0" priority="7">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(G2:G6),G2:G6,0)+1&amp;"C7",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C7",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(G2:G7),G2:G7,0)+1&amp;"C7",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C7",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
+  <conditionalFormatting sqref="H2:H7">
     <cfRule type="expression" dxfId="0" priority="8">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(H2:H6),H2:H6,0)+1&amp;"C8",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C8",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(H2:H7),H2:H7,0)+1&amp;"C8",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C8",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
+  <conditionalFormatting sqref="I2:I7">
     <cfRule type="expression" dxfId="0" priority="9">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(I2:I6),I2:I6,0)+1&amp;"C9",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C9",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(I2:I7),I2:I7,0)+1&amp;"C9",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C9",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
+  <conditionalFormatting sqref="J2:J7">
     <cfRule type="expression" dxfId="0" priority="10">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(J2:J6),J2:J6,0)+1&amp;"C10",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C10",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(J2:J7),J2:J7,0)+1&amp;"C10",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C10",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
+  <conditionalFormatting sqref="K2:K7">
     <cfRule type="expression" dxfId="0" priority="11">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(K2:K6),K2:K6,0)+1&amp;"C11",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C11",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(K2:K7),K2:K7,0)+1&amp;"C11",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C11",FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L7">
+    <cfRule type="expression" dxfId="0" priority="12">
+      <formula>INDIRECT("R"&amp;MATCH(MIN(L2:L7),L2:L7,0)+1&amp;"C12",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C12",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1520,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1554,7 +1587,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -1580,80 +1613,77 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.0963357483870714</v>
+        <v>0.09009244719999999</v>
       </c>
       <c r="D3">
-        <v>0.08933290609820875</v>
-      </c>
-      <c r="E3">
-        <v>0.06102299885779312</v>
+        <v>0.09009244719999999</v>
       </c>
       <c r="F3">
-        <v>0.0198138510140105</v>
+        <v>0.09009244719999999</v>
       </c>
       <c r="G3">
-        <v>0.2086631101782617</v>
+        <v>0.09009244719999999</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
       <c r="C4">
-        <v>0.1017868391065072</v>
+        <v>0.0963357483870714</v>
       </c>
       <c r="D4">
-        <v>0.1042305412579856</v>
+        <v>0.08933290609820875</v>
       </c>
       <c r="E4">
-        <v>0.03805194242768196</v>
+        <v>0.06102299885779312</v>
       </c>
       <c r="F4">
-        <v>0.0403536189773151</v>
+        <v>0.0198138510140105</v>
       </c>
       <c r="G4">
-        <v>0.1571001698350601</v>
+        <v>0.2086631101782617</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.6269819889146704</v>
+        <v>0.1017868391065072</v>
       </c>
       <c r="D5">
-        <v>0.5935959499733847</v>
+        <v>0.1042305412579856</v>
       </c>
       <c r="E5">
-        <v>0.3163759807530718</v>
+        <v>0.03805194242768196</v>
       </c>
       <c r="F5">
-        <v>0.3144735513157043</v>
+        <v>0.0403536189773151</v>
       </c>
       <c r="G5">
-        <v>1.38731142594779</v>
+        <v>0.1571001698350601</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -1661,28 +1691,54 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.8107173190318028</v>
+        <v>0.6269819889146704</v>
       </c>
       <c r="D6">
-        <v>0.8006220606134746</v>
+        <v>0.5935959499733847</v>
       </c>
       <c r="E6">
-        <v>0.5479263489737466</v>
+        <v>0.3163759807530718</v>
       </c>
       <c r="F6">
-        <v>0.108476024166053</v>
+        <v>0.3144735513157043</v>
       </c>
       <c r="G6">
-        <v>1.714538576347668</v>
+        <v>1.38731142594779</v>
       </c>
       <c r="H6">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>0.8107173190318028</v>
+      </c>
+      <c r="D7">
+        <v>0.8006220606134746</v>
+      </c>
+      <c r="E7">
+        <v>0.5479263489737466</v>
+      </c>
+      <c r="F7">
+        <v>0.108476024166053</v>
+      </c>
+      <c r="G7">
+        <v>1.714538576347668</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/first100/asr_report.xlsx
+++ b/outputs/first100/asr_report.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="27">
   <si>
     <t>model</t>
   </si>
@@ -36,16 +36,16 @@
     <t>qwen_audio</t>
   </si>
   <si>
+    <t>gigaam</t>
+  </si>
+  <si>
+    <t>gemma</t>
+  </si>
+  <si>
+    <t>t_one</t>
+  </si>
+  <si>
     <t>podlodka</t>
-  </si>
-  <si>
-    <t>gemma</t>
-  </si>
-  <si>
-    <t>t_one</t>
-  </si>
-  <si>
-    <t>gigaam</t>
   </si>
   <si>
     <t>golos_farfield</t>
@@ -220,25 +220,22 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>models_summary!$A$2:$A$7</c:f>
+              <c:f>models_summary!$A$2:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>gigaam</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>podlodka</c:v>
+                  <c:v>whisper</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>whisper</c:v>
+                  <c:v>t_one</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>t_one</c:v>
+                  <c:v>qwen_audio</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>qwen_audio</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>gemma</c:v>
                 </c:pt>
               </c:strCache>
@@ -246,26 +243,23 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>models_summary!$C$2:$C$7</c:f>
+              <c:f>models_summary!$C$2:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.07733205723174937</c:v>
+                  <c:v>0.07860809622857443</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.09009244719999999</c:v>
+                  <c:v>0.0963357483870714</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0963357483870714</c:v>
+                  <c:v>0.1017868391065072</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1017868391065072</c:v>
+                  <c:v>0.6269819889146704</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6269819889146704</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>0.8107173190318028</c:v>
                 </c:pt>
               </c:numCache>
@@ -676,7 +670,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>0.0758793003469506</v>
@@ -690,7 +684,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>0.4228087050189174</v>
@@ -712,7 +706,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>0.2323769898604649</v>
@@ -723,7 +717,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>0.1354387257394058</v>
@@ -756,7 +750,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -814,7 +808,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -872,7 +866,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -930,7 +924,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -988,7 +982,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -1046,7 +1040,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
@@ -1104,7 +1098,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
@@ -1162,7 +1156,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B44" t="s">
         <v>17</v>
@@ -1220,7 +1214,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B49" t="s">
         <v>18</v>
@@ -1258,10 +1252,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1272,34 +1266,31 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1309,34 +1300,34 @@
       <c r="C2">
         <v>0.108476024166053</v>
       </c>
+      <c r="D2">
+        <v>1.207452592301077</v>
+      </c>
       <c r="E2">
-        <v>1.207452592301077</v>
+        <v>0.2323769898604649</v>
       </c>
       <c r="F2">
-        <v>0.2323769898604649</v>
+        <v>1.714538576347668</v>
       </c>
       <c r="G2">
-        <v>1.714538576347668</v>
+        <v>0.3120275741794529</v>
       </c>
       <c r="H2">
-        <v>0.3120275741794529</v>
+        <v>0.7193696830116254</v>
       </c>
       <c r="I2">
-        <v>0.7193696830116254</v>
+        <v>0.8818744382153239</v>
       </c>
       <c r="J2">
-        <v>0.8818744382153239</v>
+        <v>1.204716075170621</v>
       </c>
       <c r="K2">
-        <v>1.204716075170621</v>
-      </c>
-      <c r="L2">
         <v>0.3746726475183648</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>0.0773561455379637</v>
@@ -1344,148 +1335,143 @@
       <c r="C3">
         <v>0.0856398284648606</v>
       </c>
+      <c r="D3">
+        <v>0.06935698981153519</v>
+      </c>
       <c r="E3">
-        <v>0.06935698981153519</v>
+        <v>0.09009244719999999</v>
+      </c>
+      <c r="F3">
+        <v>0.181590372425242</v>
       </c>
       <c r="G3">
-        <v>0.181590372425242</v>
+        <v>0.0157007974219522</v>
       </c>
       <c r="H3">
-        <v>0.0157007974219522</v>
+        <v>0.0569488535940136</v>
       </c>
       <c r="I3">
-        <v>0.0569488535940136</v>
+        <v>0.1012309764608291</v>
       </c>
       <c r="J3">
-        <v>0.1012309764608291</v>
+        <v>0.0539121372454705</v>
       </c>
       <c r="K3">
-        <v>0.0539121372454705</v>
-      </c>
-      <c r="L3">
         <v>0.0542524141238774</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>0.398678369890491</v>
+      </c>
+      <c r="C4">
+        <v>0.3144735513157043</v>
       </c>
       <c r="D4">
-        <v>0.09009244719999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1.38731142594779</v>
+      </c>
+      <c r="E4">
+        <v>0.4228087050189174</v>
+      </c>
+      <c r="F4">
+        <v>0.6201261735947166</v>
+      </c>
+      <c r="G4">
+        <v>0.5670657263520529</v>
+      </c>
+      <c r="H4">
+        <v>0.6451614902183401</v>
+      </c>
+      <c r="I4">
+        <v>0.8665847061955988</v>
+      </c>
+      <c r="J4">
+        <v>0.6796962577265608</v>
+      </c>
+      <c r="K4">
+        <v>0.3679134828865326</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>0.398678369890491</v>
+        <v>0.08837812019630201</v>
       </c>
       <c r="C5">
-        <v>0.3144735513157043</v>
+        <v>0.1169500122170223</v>
+      </c>
+      <c r="D5">
+        <v>0.1315419709359103</v>
       </c>
       <c r="E5">
-        <v>1.38731142594779</v>
+        <v>0.1354387257394058</v>
       </c>
       <c r="F5">
-        <v>0.4228087050189174</v>
+        <v>0.1571001698350601</v>
       </c>
       <c r="G5">
-        <v>0.6201261735947166</v>
+        <v>0.0403536189773151</v>
       </c>
       <c r="H5">
-        <v>0.5670657263520529</v>
+        <v>0.0481800055224305</v>
       </c>
       <c r="I5">
-        <v>0.6451614902183401</v>
+        <v>0.1239483357364959</v>
       </c>
       <c r="J5">
-        <v>0.8665847061955988</v>
+        <v>0.091511070298949</v>
       </c>
       <c r="K5">
-        <v>0.6796962577265608</v>
-      </c>
-      <c r="L5">
-        <v>0.3679134828865326</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>0.0844663616061808</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0.08837812019630201</v>
+        <v>0.1206278569914933</v>
       </c>
       <c r="C6">
-        <v>0.1169500122170223</v>
+        <v>0.0431007612221763</v>
+      </c>
+      <c r="D6">
+        <v>0.2086631101782617</v>
       </c>
       <c r="E6">
-        <v>0.1315419709359103</v>
+        <v>0.0758793003469506</v>
       </c>
       <c r="F6">
-        <v>0.1354387257394058</v>
+        <v>0.1321356768181972</v>
       </c>
       <c r="G6">
-        <v>0.1571001698350601</v>
+        <v>0.0261487014625819</v>
       </c>
       <c r="H6">
-        <v>0.0403536189773151</v>
+        <v>0.1027865118494669</v>
       </c>
       <c r="I6">
-        <v>0.0481800055224305</v>
+        <v>0.1623050360302916</v>
       </c>
       <c r="J6">
-        <v>0.1239483357364959</v>
+        <v>0.07189667795728399</v>
       </c>
       <c r="K6">
-        <v>0.091511070298949</v>
-      </c>
-      <c r="L6">
-        <v>0.0844663616061808</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>0.1206278569914933</v>
-      </c>
-      <c r="C7">
-        <v>0.0431007612221763</v>
-      </c>
-      <c r="E7">
-        <v>0.2086631101782617</v>
-      </c>
-      <c r="F7">
-        <v>0.0758793003469506</v>
-      </c>
-      <c r="G7">
-        <v>0.1321356768181972</v>
-      </c>
-      <c r="H7">
-        <v>0.0261487014625819</v>
-      </c>
-      <c r="I7">
-        <v>0.1027865118494669</v>
-      </c>
-      <c r="J7">
-        <v>0.1623050360302916</v>
-      </c>
-      <c r="K7">
-        <v>0.07189667795728399</v>
-      </c>
-      <c r="L7">
         <v>0.0198138510140105</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B6">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(B2:B7),B2:B7,0)+1&amp;"C2",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C2",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(B2:B6),B2:B6,0)+1&amp;"C2",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C2",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:L7">
+  <conditionalFormatting sqref="B2:K6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1497,54 +1483,49 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C7">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(C2:C7),C2:C7,0)+1&amp;"C3",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C3",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(C2:C6),C2:C6,0)+1&amp;"C3",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C3",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D6">
     <cfRule type="expression" dxfId="0" priority="4">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(D2:D7),D2:D7,0)+1&amp;"C4",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C4",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(D2:D6),D2:D6,0)+1&amp;"C4",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C4",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E6">
     <cfRule type="expression" dxfId="0" priority="5">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(E2:E7),E2:E7,0)+1&amp;"C5",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C5",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(E2:E6),E2:E6,0)+1&amp;"C5",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C5",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F6">
     <cfRule type="expression" dxfId="0" priority="6">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(F2:F7),F2:F7,0)+1&amp;"C6",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C6",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(F2:F6),F2:F6,0)+1&amp;"C6",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C6",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="0" priority="7">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(G2:G7),G2:G7,0)+1&amp;"C7",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C7",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(G2:G6),G2:G6,0)+1&amp;"C7",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C7",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H6">
     <cfRule type="expression" dxfId="0" priority="8">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(H2:H7),H2:H7,0)+1&amp;"C8",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C8",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(H2:H6),H2:H6,0)+1&amp;"C8",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C8",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I6">
     <cfRule type="expression" dxfId="0" priority="9">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(I2:I7),I2:I7,0)+1&amp;"C9",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C9",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(I2:I6),I2:I6,0)+1&amp;"C9",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C9",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
+  <conditionalFormatting sqref="J2:J6">
     <cfRule type="expression" dxfId="0" priority="10">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(J2:J7),J2:J7,0)+1&amp;"C10",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C10",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(J2:J6),J2:J6,0)+1&amp;"C10",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C10",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
+  <conditionalFormatting sqref="K2:K6">
     <cfRule type="expression" dxfId="0" priority="11">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(K2:K7),K2:K7,0)+1&amp;"C11",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C11",FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
-    <cfRule type="expression" dxfId="0" priority="12">
-      <formula>INDIRECT("R"&amp;MATCH(MIN(L2:L7),L2:L7,0)+1&amp;"C12",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C12",FALSE)</formula>
+      <formula>INDIRECT("R"&amp;MATCH(MIN(K2:K6),K2:K6,0)+1&amp;"C11",FALSE)=INDIRECT("R"&amp;ROW()&amp;"C11",FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1553,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1587,19 +1568,19 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>0.07733205723174937</v>
+        <v>0.07860809622857443</v>
       </c>
       <c r="D2">
-        <v>0.06935698981153519</v>
+        <v>0.07335656767474945</v>
       </c>
       <c r="E2">
-        <v>0.04591925756858373</v>
+        <v>0.04348073714253898</v>
       </c>
       <c r="F2">
         <v>0.0157007974219522</v>
@@ -1613,77 +1594,80 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>0.09009244719999999</v>
+        <v>0.0963357483870714</v>
       </c>
       <c r="D3">
-        <v>0.09009244719999999</v>
+        <v>0.08933290609820875</v>
+      </c>
+      <c r="E3">
+        <v>0.06102299885779312</v>
       </c>
       <c r="F3">
-        <v>0.09009244719999999</v>
+        <v>0.0198138510140105</v>
       </c>
       <c r="G3">
-        <v>0.09009244719999999</v>
+        <v>0.2086631101782617</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
       <c r="C4">
-        <v>0.0963357483870714</v>
+        <v>0.1017868391065072</v>
       </c>
       <c r="D4">
-        <v>0.08933290609820875</v>
+        <v>0.1042305412579856</v>
       </c>
       <c r="E4">
-        <v>0.06102299885779312</v>
+        <v>0.03805194242768196</v>
       </c>
       <c r="F4">
-        <v>0.0198138510140105</v>
+        <v>0.0403536189773151</v>
       </c>
       <c r="G4">
-        <v>0.2086631101782617</v>
+        <v>0.1571001698350601</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.1017868391065072</v>
+        <v>0.6269819889146704</v>
       </c>
       <c r="D5">
-        <v>0.1042305412579856</v>
+        <v>0.5935959499733847</v>
       </c>
       <c r="E5">
-        <v>0.03805194242768196</v>
+        <v>0.3163759807530718</v>
       </c>
       <c r="F5">
-        <v>0.0403536189773151</v>
+        <v>0.3144735513157043</v>
       </c>
       <c r="G5">
-        <v>0.1571001698350601</v>
+        <v>1.38731142594779</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -1691,54 +1675,28 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.6269819889146704</v>
+        <v>0.8107173190318028</v>
       </c>
       <c r="D6">
-        <v>0.5935959499733847</v>
+        <v>0.8006220606134746</v>
       </c>
       <c r="E6">
-        <v>0.3163759807530718</v>
+        <v>0.5479263489737466</v>
       </c>
       <c r="F6">
-        <v>0.3144735513157043</v>
+        <v>0.108476024166053</v>
       </c>
       <c r="G6">
-        <v>1.38731142594779</v>
+        <v>1.714538576347668</v>
       </c>
       <c r="H6">
         <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>0.8107173190318028</v>
-      </c>
-      <c r="D7">
-        <v>0.8006220606134746</v>
-      </c>
-      <c r="E7">
-        <v>0.5479263489737466</v>
-      </c>
-      <c r="F7">
-        <v>0.108476024166053</v>
-      </c>
-      <c r="G7">
-        <v>1.714538576347668</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
